--- a/argus/kship/models/086670_model.xlsx
+++ b/argus/kship/models/086670_model.xlsx
@@ -654,55 +654,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 199298억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−1) 199299억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 209380억 × 비례계수 0.0098 × 계절비중 Q1 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−1) 209445억 × 비례계수 0.0098 × 계절비중 Q1 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 216860억 × 비례계수 0.0098 × 계절비중 Q2 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−1) 216987억 × 비례계수 0.0098 × 계절비중 Q2 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 214100억 × 비례계수 0.0098 × 계절비중 Q3 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−1) 214689억 × 비례계수 0.0098 × 계절비중 Q3 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 213215억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−1) 213857억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 211345억 × 비례계수 0.0098 × 계절비중 Q1 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−1) 211978억 × 비례계수 0.0098 × 계절비중 Q1 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 208804억 × 비례계수 0.0098 × 계절비중 Q2 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−1) 209429억 × 비례계수 0.0098 × 계절비중 Q2 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 201999억 × 비례계수 0.0098 × 계절비중 Q3 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−1) 202215억 × 비례계수 0.0098 × 계절비중 Q3 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 190830억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−1) 191046억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -918,7 +918,7 @@
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 278억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 279억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
@@ -930,13 +930,13 @@
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 352억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 353억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 331억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 332억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
@@ -1701,55 +1701,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 199298억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−1) 199299억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 209380억 × 비례계수 0.0098 × 계절비중 Q1 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−1) 209445억 × 비례계수 0.0098 × 계절비중 Q1 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 216860억 × 비례계수 0.0098 × 계절비중 Q2 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−1) 216987억 × 비례계수 0.0098 × 계절비중 Q2 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 214100억 × 비례계수 0.0098 × 계절비중 Q3 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−1) 214689억 × 비례계수 0.0098 × 계절비중 Q3 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 213215억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−1) 213857억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 211345억 × 비례계수 0.0098 × 계절비중 Q1 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−1) 211978억 × 비례계수 0.0098 × 계절비중 Q1 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 208804억 × 비례계수 0.0098 × 계절비중 Q2 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−1) 209429억 × 비례계수 0.0098 × 계절비중 Q2 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 201999억 × 비례계수 0.0098 × 계절비중 Q3 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−1) 202215억 × 비례계수 0.0098 × 계절비중 Q3 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 190830억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−1) 191046억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2180,7 +2180,7 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 278억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 279억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -2192,13 +2192,13 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 352억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 353억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 331억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 332억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -6328,29 +6328,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.426317</v>
+        <v>0.426767</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.168805</v>
+        <v>0.169484</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.155235</v>
+        <v>0.158436</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.06981999999999999</v>
+        <v>0.07305399999999999</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.009382</v>
+        <v>0.012099</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.037145</v>
+        <v>-0.034838</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.0565</v>
+        <v>-0.05811</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.104977</v>
+        <v>-0.10667</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6477,32 +6477,32 @@
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.144167</v>
+        <v>0.14416</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.144164</v>
+        <v>0.144168</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.144167</v>
+        <v>0.144163</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.144169</v>
+        <v>0.144162</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.144174</v>
+        <v>0.14417</v>
       </c>
       <c r="AL22" s="24" t="n">
+        <v>0.144163</v>
+      </c>
+      <c r="AM22" s="24" t="n">
+        <v>0.144168</v>
+      </c>
+      <c r="AN22" s="24" t="n">
         <v>0.144172</v>
-      </c>
-      <c r="AM22" s="24" t="n">
-        <v>0.144166</v>
-      </c>
-      <c r="AN22" s="24" t="n">
-        <v>0.144168</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6632,32 +6632,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.081446</v>
+        <v>0.08144</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.08144700000000001</v>
+        <v>0.081453</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.081438</v>
+        <v>0.081441</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.081444</v>
+        <v>0.08144</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.081451</v>
+        <v>0.08144</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.08144700000000001</v>
+        <v>0.081442</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.08143400000000001</v>
+        <v>0.08143599999999999</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.081446</v>
+        <v>0.081438</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7216,32 +7216,32 @@
         <v/>
       </c>
       <c r="AF27" s="24" t="n">
-        <v>0.172785</v>
+        <v>0.172744</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.17278</v>
+        <v>0.172881</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.172736</v>
+        <v>0.172761</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.172907</v>
+        <v>0.172815</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.172729</v>
+        <v>0.172941</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.172789</v>
+        <v>0.172737</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.172909</v>
+        <v>0.172732</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.172872</v>
+        <v>0.172905</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7636,13 +7636,13 @@
         <v>0</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>59.56</v>
+        <v>59.55</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
@@ -7652,7 +7652,7 @@
         <v>59.56</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AN30" s="29" t="n">
         <v>0</v>
@@ -7764,13 +7764,13 @@
         <v>0</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>59.56</v>
+        <v>59.55</v>
       </c>
       <c r="AH31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
@@ -7780,7 +7780,7 @@
         <v>59.56</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AN31" s="29" t="n">
         <v>0</v>
@@ -8105,29 +8105,29 @@
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.154262</v>
+        <v>0.154306</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.075058</v>
+        <v>-0.074979</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.137303</v>
+        <v>0.137654</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.134875</v>
+        <v>0.135212</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.114384</v>
+        <v>0.114649</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.059144</v>
+        <v>-0.058775</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.097326</v>
+        <v>0.097285</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.094084</v>
+        <v>0.09407</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8766,26 +8766,26 @@
         <v>0.981846</v>
       </c>
       <c r="AG40" s="24" t="n">
-        <v>1.061947</v>
+        <v>1.060472</v>
       </c>
       <c r="AH40" s="24" t="n">
-        <v>-0.080952</v>
+        <v>-0.081633</v>
       </c>
       <c r="AI40" s="24" t="n">
-        <v>0.021572</v>
+        <v>0.01926</v>
       </c>
       <c r="AJ40" s="25" t="n"/>
       <c r="AK40" s="24" t="n">
-        <v>0.00687</v>
+        <v>0.00458</v>
       </c>
       <c r="AL40" s="24" t="n">
-        <v>-0.050787</v>
+        <v>-0.052971</v>
       </c>
       <c r="AM40" s="24" t="n">
-        <v>-0.008142</v>
+        <v>-0.01037</v>
       </c>
       <c r="AN40" s="24" t="n">
-        <v>0.033937</v>
+        <v>0.034769</v>
       </c>
       <c r="AO40" s="25" t="n"/>
     </row>
@@ -9186,32 +9186,32 @@
         <v/>
       </c>
       <c r="AF43" s="24" t="n">
-        <v>0.081446</v>
+        <v>0.08144</v>
       </c>
       <c r="AG43" s="24" t="n">
-        <v>0.08144700000000001</v>
+        <v>0.081453</v>
       </c>
       <c r="AH43" s="24" t="n">
-        <v>0.081438</v>
+        <v>0.081441</v>
       </c>
       <c r="AI43" s="24" t="n">
-        <v>0.081444</v>
+        <v>0.08144</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ34/subQ!AJ33,"")</f>
         <v/>
       </c>
       <c r="AK43" s="24" t="n">
-        <v>0.081451</v>
+        <v>0.08144</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>0.08144700000000001</v>
+        <v>0.081442</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>0.08143400000000001</v>
+        <v>0.08143599999999999</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>0.081446</v>
+        <v>0.081438</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO34/subQ!AO33,"")</f>
@@ -39398,7 +39398,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1397.3</v>
+        <v>1397.6</v>
       </c>
     </row>
     <row r="30">
@@ -39418,7 +39418,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.98</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="32">
@@ -39438,7 +39438,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.0912</v>
+        <v>0.09130000000000001</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/086670_model.xlsx
+++ b/argus/kship/models/086670_model.xlsx
@@ -648,61 +648,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 185329억 × 비례계수 0.0098 × 계절비중 Q3 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+전년동기 × (1+7.3%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 199299억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+전년동기 × (1+7.3%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 209445억 × 비례계수 0.0098 × 계절비중 Q1 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+전년동기 × (1+7.3%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 216987억 × 비례계수 0.0098 × 계절비중 Q2 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+전년동기 × (1+7.3%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 214689억 × 비례계수 0.0098 × 계절비중 Q3 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+전년동기 × (1+3.6%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 213857억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+전년동기 × (1+3.6%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 211978억 × 비례계수 0.0098 × 계절비중 Q1 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+전년동기 × (1+3.6%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 209429억 × 비례계수 0.0098 × 계절비중 Q2 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+전년동기 × (1+3.6%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 202215억 × 비례계수 0.0098 × 계절비중 Q3 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+전년동기 × (1+1.8%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−1) 191046억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+전년동기 × (1+1.8%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -768,121 +768,121 @@
     <comment ref="AC23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AD23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AF23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AG23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AH23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AI23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AK23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AL23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AM23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AN23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AC24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.1% 유지</t>
+최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AD24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.1% 유지</t>
+최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AF24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.1% 유지</t>
+최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AG24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.1% 유지</t>
+최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AH24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.1% 유지</t>
+최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AI24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.1% 유지</t>
+최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AK24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.1% 유지</t>
+최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AL24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.1% 유지</t>
+최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AM24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.1% 유지</t>
+최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AN24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 8.1% 유지</t>
+최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AC25" authorId="0" shapeId="0">
@@ -894,55 +894,55 @@
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 195억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 194억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 229억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 219억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 265억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 246억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 245억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 223억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 279억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 252억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 316억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 278억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 353억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 307억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 332억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 285억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 364억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 315억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1695,61 +1695,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 185329억 × 비례계수 0.0098 × 계절비중 Q3 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 전년동기 × (1+7.3%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 199299억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 전년동기 × (1+7.3%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 209445억 × 비례계수 0.0098 × 계절비중 Q1 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 전년동기 × (1+7.3%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 216987억 × 비례계수 0.0098 × 계절비중 Q2 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 전년동기 × (1+7.3%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 214689억 × 비례계수 0.0098 × 계절비중 Q3 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 전년동기 × (1+3.6%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 213857억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 전년동기 × (1+3.6%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 211978억 × 비례계수 0.0098 × 계절비중 Q1 0.247(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 전년동기 × (1+3.6%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 209429억 × 비례계수 0.0098 × 계절비중 Q2 0.268(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 전년동기 × (1+3.6%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 202215억 × 비례계수 0.0098 × 계절비중 Q3 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 전년동기 × (1+1.8%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−1) 191046억 × 비례계수 0.0098 × 계절비중 Q4 0.256(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: 전년동기 × (1+1.8%) — g=최근 4분기 합 YoY 7.3% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
@@ -1935,61 +1935,61 @@
     </comment>
     <comment ref="AC9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AF9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AH9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AK9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
@@ -2090,61 +2090,61 @@
     </comment>
     <comment ref="AC10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 8.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 8.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
@@ -2156,55 +2156,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 195억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 194억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 229억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 219억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 265억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 246억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 245억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 223억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 279억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 252억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 316억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 278억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 353억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 307억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 332억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 285억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 364억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 315억 × 2.53% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4145,7 +4145,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4266,14 +4266,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 14.7% &gt; 추세 11.6% × 1.10 (suppliers_mentions·시차 1·4분기 이동합·창 8, r=0.91 유의)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 11.6, "op_wape_pct": 52.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 359.49, "rev_act": 374.64, "op_pred": 21.1, "op_act": 58.13}, {"q": "2025Q4", "rev_pred": 399.64, "rev_act": 336.61, "op_pred": 23.45, "op_act": 33.07}, {"q": "2026Q1", "rev_pred": 402.89, "rev_act": 355.69, "op_pred": 23.64, "op_act": 17.72}, {"q": "2026Q2", "rev_pred": 432.3, "rev_act": 486.47, "op_pred": 25.37, "op_act": 62.96}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 11.6, "op_wape_pct": 52.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"wape_link": null, "wape_trend": null, "adopted": false, "note": "유의성 조건 미달 → OOS 비교 전 기각"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 359.49, "rev_act": 374.64, "op_pred": 21.1, "op_act": 58.13}, {"q": "2025Q4", "rev_pred": 399.64, "rev_act": 336.61, "op_pred": 23.45, "op_act": 33.07}, {"q": "2026Q1", "rev_pred": 402.89, "rev_act": 355.69, "op_pred": 23.64, "op_act": 17.72}, {"q": "2026Q2", "rev_pred": 432.3, "rev_act": 486.47, "op_pred": 25.37, "op_act": 62.96}]}</t>
         </is>
       </c>
     </row>
@@ -6321,36 +6321,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.109077</v>
+        <v>0.072615</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.487951</v>
+        <v>0.072604</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.426767</v>
+        <v>0.072613</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.169484</v>
+        <v>0.07262299999999999</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.158436</v>
+        <v>0.036308</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.07305399999999999</v>
+        <v>0.036311</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.012099</v>
+        <v>0.036302</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.034838</v>
+        <v>0.036297</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.05811</v>
+        <v>0.018154</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.10667</v>
+        <v>0.018174</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6467,10 +6467,10 @@
         <v/>
       </c>
       <c r="AC22" s="24" t="n">
-        <v>0.144164</v>
+        <v>0.144162</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.144172</v>
+        <v>0.144163</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
@@ -6480,29 +6480,29 @@
         <v>0.14416</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.144168</v>
+        <v>0.144155</v>
       </c>
       <c r="AH22" s="24" t="n">
+        <v>0.144154</v>
+      </c>
+      <c r="AI22" s="24" t="n">
         <v>0.144163</v>
-      </c>
-      <c r="AI22" s="24" t="n">
-        <v>0.144162</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.14417</v>
+        <v>0.144169</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.144163</v>
+        <v>0.144173</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.144168</v>
+        <v>0.144154</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.144172</v>
+        <v>0.144162</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6622,42 +6622,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.081444</v>
+        <v>0.08144999999999999</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.08144</v>
+        <v>0.081457</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.08144</v>
+        <v>0.081437</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.081453</v>
+        <v>0.08144899999999999</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.081441</v>
+        <v>0.081454</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.08144</v>
+        <v>0.08143599999999999</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.08144</v>
+        <v>0.081443</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.081442</v>
+        <v>0.081444</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.08143599999999999</v>
+        <v>0.081441</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.081438</v>
+        <v>0.081452</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -6906,32 +6906,32 @@
         <v/>
       </c>
       <c r="AF25" s="29" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7206,42 +7206,42 @@
         <v/>
       </c>
       <c r="AC27" s="24" t="n">
-        <v>0.172829</v>
+        <v>0.172883</v>
       </c>
       <c r="AD27" s="24" t="n">
-        <v>0.172775</v>
+        <v>0.172706</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE14/subQ!AE13,"")</f>
         <v/>
       </c>
       <c r="AF27" s="24" t="n">
-        <v>0.172744</v>
+        <v>0.172828</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.172881</v>
+        <v>0.172758</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.172761</v>
+        <v>0.172658</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.172815</v>
+        <v>0.172747</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.172941</v>
+        <v>0.17285</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.172737</v>
+        <v>0.172901</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.172732</v>
+        <v>0.172812</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.172905</v>
+        <v>0.172925</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AG30" s="29" t="n">
         <v>59.55</v>
@@ -7642,20 +7642,20 @@
         <v>0</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>59.56</v>
+        <v>59.55</v>
       </c>
       <c r="AM30" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -7757,11 +7757,11 @@
         <v>-0.0026</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AG31" s="29" t="n">
         <v>59.55</v>
@@ -7770,17 +7770,17 @@
         <v>0</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>59.56</v>
+        <v>59.55</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN31" s="29" t="n">
         <v>0</v>
@@ -8098,36 +8098,36 @@
         <v/>
       </c>
       <c r="AC34" s="24" t="n">
-        <v>0.174171</v>
+        <v>0.168559</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.178632</v>
+        <v>0.130848</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.154306</v>
+        <v>0.122603</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>-0.074979</v>
+        <v>-0.094</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.137654</v>
+        <v>0.131184</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.135212</v>
+        <v>0.105255</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.114649</v>
+        <v>0.100905</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>-0.058775</v>
+        <v>-0.07019400000000001</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.097285</v>
+        <v>0.105416</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.09407</v>
+        <v>0.0867</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8756,36 +8756,36 @@
         <v/>
       </c>
       <c r="AC40" s="24" t="n">
-        <v>2.114407</v>
+        <v>2.135593</v>
       </c>
       <c r="AD40" s="24" t="n">
-        <v>1.100324</v>
+        <v>1.257282</v>
       </c>
       <c r="AE40" s="25" t="n"/>
       <c r="AF40" s="24" t="n">
-        <v>0.981846</v>
+        <v>1.270802</v>
       </c>
       <c r="AG40" s="24" t="n">
-        <v>1.060472</v>
+        <v>1.452802</v>
       </c>
       <c r="AH40" s="24" t="n">
-        <v>-0.081633</v>
+        <v>0.111486</v>
       </c>
       <c r="AI40" s="24" t="n">
-        <v>0.01926</v>
+        <v>0.167742</v>
       </c>
       <c r="AJ40" s="25" t="n"/>
       <c r="AK40" s="24" t="n">
-        <v>0.00458</v>
+        <v>0.073951</v>
       </c>
       <c r="AL40" s="24" t="n">
-        <v>-0.052971</v>
+        <v>-0.043295</v>
       </c>
       <c r="AM40" s="24" t="n">
-        <v>-0.01037</v>
+        <v>-0.039514</v>
       </c>
       <c r="AN40" s="24" t="n">
-        <v>0.034769</v>
+        <v>-0.036219</v>
       </c>
       <c r="AO40" s="25" t="n"/>
     </row>
@@ -8878,33 +8878,33 @@
         <v>0.736111</v>
       </c>
       <c r="AD41" s="24" t="n">
-        <v>0.487805</v>
+        <v>0.5</v>
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="24" t="n">
-        <v>0.363636</v>
+        <v>0.375</v>
       </c>
       <c r="AG41" s="24" t="n">
-        <v>0.174757</v>
+        <v>0.194175</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>-0.048</v>
+        <v>-0.032</v>
       </c>
       <c r="AI41" s="24" t="n">
-        <v>-0.04918</v>
+        <v>-0.03252</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>-0.05</v>
+        <v>-0.033058</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>-0.049587</v>
+        <v>-0.04065</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>-0.05042</v>
+        <v>-0.041322</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>-0.043103</v>
+        <v>-0.042017</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -9176,42 +9176,42 @@
         <v/>
       </c>
       <c r="AC43" s="24" t="n">
-        <v>0.081444</v>
+        <v>0.08144999999999999</v>
       </c>
       <c r="AD43" s="24" t="n">
-        <v>0.08144</v>
+        <v>0.081457</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE34/subQ!AE33,"")</f>
         <v/>
       </c>
       <c r="AF43" s="24" t="n">
-        <v>0.08144</v>
+        <v>0.081437</v>
       </c>
       <c r="AG43" s="24" t="n">
-        <v>0.081453</v>
+        <v>0.08144899999999999</v>
       </c>
       <c r="AH43" s="24" t="n">
-        <v>0.081441</v>
+        <v>0.081454</v>
       </c>
       <c r="AI43" s="24" t="n">
-        <v>0.08144</v>
+        <v>0.08143599999999999</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ34/subQ!AJ33,"")</f>
         <v/>
       </c>
       <c r="AK43" s="24" t="n">
-        <v>0.08144</v>
+        <v>0.081443</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>0.081442</v>
+        <v>0.081444</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>0.08143599999999999</v>
+        <v>0.081441</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>0.081438</v>
+        <v>0.081452</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO34/subQ!AO33,"")</f>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39398,7 +39398,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1397.6</v>
+        <v>1174.4</v>
       </c>
     </row>
     <row r="30">
@@ -39418,7 +39418,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.97</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="32">
@@ -39438,7 +39438,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.0767</v>
       </c>
     </row>
     <row r="34">
@@ -39448,7 +39448,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="35">
@@ -39458,7 +39458,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15500</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/086670_model.xlsx
+++ b/argus/kship/models/086670_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4214,7 +4214,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5085,35 +5085,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5204,35 +5204,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5323,35 +5323,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5442,35 +5442,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5561,35 +5561,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5680,35 +5680,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5799,35 +5799,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5918,35 +5918,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6053,7 +6053,7 @@
         <v>19100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18890</v>
+        <v>19450</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6326,7 +6326,7 @@
         <v>16264.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19055</v>
+        <v>19186.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9208,7 +9208,7 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>18890</v>
+        <v>19450</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33785,7 +33785,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38918,7 +38918,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41058,7 +41058,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.08</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="32">
@@ -41068,7 +41068,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/086670_model.xlsx
+++ b/argus/kship/models/086670_model.xlsx
@@ -4214,7 +4214,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5085,35 +5085,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5204,35 +5204,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5323,35 +5323,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5442,35 +5442,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5561,35 +5561,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5680,35 +5680,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5799,35 +5799,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5918,35 +5918,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6053,7 +6053,7 @@
         <v>19100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>19450</v>
+        <v>18910</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6144,7 +6144,7 @@
         <v>19740</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>19600</v>
+        <v>19690</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6326,7 +6326,7 @@
         <v>16264.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19186.7</v>
+        <v>19160</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9208,11 +9208,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>19450</v>
+        <v>18910</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,050원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,940원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33785,7 +33785,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38918,7 +38918,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41058,7 +41058,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.56</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="32">
@@ -41068,7 +41068,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/086670_model.xlsx
+++ b/argus/kship/models/086670_model.xlsx
@@ -4214,7 +4214,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/086670_model.xlsx
+++ b/argus/kship/models/086670_model.xlsx
@@ -5085,35 +5085,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5204,35 +5204,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5323,35 +5323,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5442,35 +5442,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5561,35 +5561,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5680,35 +5680,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5799,35 +5799,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5918,35 +5918,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6053,7 +6053,7 @@
         <v>19100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18910</v>
+        <v>18820</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6144,7 +6144,7 @@
         <v>19740</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>19690</v>
+        <v>19820</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6235,7 +6235,7 @@
         <v>13000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>18680</v>
+        <v>18670</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6326,7 +6326,7 @@
         <v>16264.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19160</v>
+        <v>19088</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9208,11 +9208,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>18910</v>
+        <v>18820</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,940원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,530원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -33785,7 +33785,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38918,7 +38918,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41058,7 +41058,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.1</v>
+        <v>16.03</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/086670_model.xlsx
+++ b/argus/kship/models/086670_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4214,7 +4214,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/086670_model.xlsx
+++ b/argus/kship/models/086670_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -5085,35 +5085,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5204,35 +5204,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5323,35 +5323,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5442,35 +5442,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5561,35 +5561,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5680,35 +5680,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5799,35 +5799,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5918,35 +5918,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6053,7 +6053,7 @@
         <v>19100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18820</v>
+        <v>18840</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6326,7 +6326,7 @@
         <v>16264.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19088</v>
+        <v>19092</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9208,11 +9208,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>18820</v>
+        <v>18840</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,530원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,900원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -41058,7 +41058,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.03</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/086670_model.xlsx
+++ b/argus/kship/models/086670_model.xlsx
@@ -4214,7 +4214,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5085,35 +5085,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5204,35 +5204,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5323,35 +5323,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5442,35 +5442,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5561,35 +5561,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5680,35 +5680,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5799,35 +5799,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5918,35 +5918,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/086670_model.xlsx
+++ b/argus/kship/models/086670_model.xlsx
@@ -4214,7 +4214,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/086670_model.xlsx
+++ b/argus/kship/models/086670_model.xlsx
@@ -4214,7 +4214,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
         <v>19100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18840</v>
+        <v>18460</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6235,7 +6235,7 @@
         <v>13000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>18670</v>
+        <v>18310</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6326,7 +6326,7 @@
         <v>16264.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19092</v>
+        <v>18986.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9208,7 +9208,7 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>18840</v>
+        <v>18460</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33785,7 +33785,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38918,7 +38918,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41058,7 +41058,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.04</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="32">
@@ -41068,7 +41068,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/086670_model.xlsx
+++ b/argus/kship/models/086670_model.xlsx
@@ -4214,7 +4214,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5085,35 +5085,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5204,35 +5204,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5323,35 +5323,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5442,35 +5442,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5561,35 +5561,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5680,35 +5680,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5799,35 +5799,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5918,35 +5918,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6053,7 +6053,7 @@
         <v>19100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18460</v>
+        <v>17880</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6235,7 +6235,7 @@
         <v>13000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>18310</v>
+        <v>17210</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6326,7 +6326,7 @@
         <v>16264.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>18986.7</v>
+        <v>18821.4</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9208,11 +9208,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>18460</v>
+        <v>17880</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,900원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,880원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33785,7 +33785,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38918,7 +38918,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41058,7 +41058,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.72</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="32">
@@ -41068,7 +41068,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/086670_model.xlsx
+++ b/argus/kship/models/086670_model.xlsx
@@ -4214,7 +4214,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5085,35 +5085,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5204,35 +5204,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5323,35 +5323,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5442,35 +5442,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5561,35 +5561,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5680,35 +5680,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5799,35 +5799,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5918,35 +5918,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6053,7 +6053,7 @@
         <v>19100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>17880</v>
+        <v>17320</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6235,7 +6235,7 @@
         <v>13000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>17210</v>
+        <v>17030</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6326,7 +6326,7 @@
         <v>16264.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>18821.4</v>
+        <v>18648.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9208,11 +9208,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>17880</v>
+        <v>17320</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,880원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,440원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33785,7 +33785,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38918,7 +38918,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41058,7 +41058,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.22</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="32">
@@ -41068,7 +41068,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/086670_model.xlsx
+++ b/argus/kship/models/086670_model.xlsx
@@ -4214,7 +4214,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5085,35 +5085,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5204,35 +5204,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5323,35 +5323,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5442,35 +5442,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5561,35 +5561,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5680,35 +5680,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5799,35 +5799,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5918,35 +5918,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6053,7 +6053,7 @@
         <v>19100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>17320</v>
+        <v>16510</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6235,7 +6235,7 @@
         <v>13000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>17030</v>
+        <v>15910</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6326,7 +6326,7 @@
         <v>16264.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>18648.8</v>
+        <v>18061.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9208,11 +9208,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>17320</v>
+        <v>16510</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,440원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,300원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33785,7 +33785,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38918,7 +38918,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41058,7 +41058,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.75</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="32">
@@ -41068,7 +41068,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/086670_model.xlsx
+++ b/argus/kship/models/086670_model.xlsx
@@ -4214,7 +4214,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5085,35 +5085,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5204,35 +5204,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5323,35 +5323,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5442,35 +5442,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5561,35 +5561,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5680,35 +5680,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5799,35 +5799,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5918,35 +5918,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6053,7 +6053,7 @@
         <v>19100</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>16510</v>
+        <v>15880</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6235,7 +6235,7 @@
         <v>13000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>15910</v>
+        <v>15410</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6326,7 +6326,7 @@
         <v>16264.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>18061.8</v>
+        <v>17553.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9208,11 +9208,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>16510</v>
+        <v>15880</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,300원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,560원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33785,7 +33785,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38918,7 +38918,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41058,7 +41058,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.06</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="32">
@@ -41068,7 +41068,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="33">
